--- a/docs/downloads/10/tbl_ef_vente_marovoay_tous.xlsx
+++ b/docs/downloads/10/tbl_ef_vente_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -405,7 +405,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -426,7 +426,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -468,7 +468,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -570,7 +570,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -612,7 +612,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
